--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487926_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487926_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0176</v>
+        <v>6.1425</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9832</v>
+        <v>3.5779</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0343</v>
+        <v>2.5646</v>
       </c>
       <c r="G2" t="n">
         <v>3.0844</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6657</v>
+        <v>1.7907</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2388</v>
+        <v>0.8335</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4269</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8137</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9502</v>
+        <v>2.2232</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4284</v>
+        <v>1.6427</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5218</v>
+        <v>0.5805</v>
       </c>
       <c r="G3" t="n">
         <v>1.8973</v>
@@ -688,13 +688,13 @@
         <v>0.2081</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0385</v>
+        <v>0.2345</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2486</v>
+        <v>-0.0343</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2101</v>
+        <v>0.2688</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1168</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.225</v>
+        <v>-0.4574</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.354</v>
+        <v>0.1263</v>
       </c>
       <c r="F4" t="n">
-        <v>2.129</v>
+        <v>-0.5838</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0771</v>
+        <v>-0.5646</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3564</v>
+        <v>-0.1727</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2793</v>
+        <v>-0.3919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4702</v>
+        <v>0.0192</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4826</v>
+        <v>0.0192</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9527</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5473</v>
+        <v>-0.5838</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8738</v>
+        <v>-0.1919</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3266</v>
+        <v>-0.3919</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7876</v>
+        <v>0.1072</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5244</v>
+        <v>0.1072</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2632</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5646</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0192</v>
+        <v>0.3544</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5838</v>
+        <v>-1.2218</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5646</v>
+        <v>-1.5655</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1727</v>
+        <v>-0.1066</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3919</v>
+        <v>-1.4589</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0192</v>
+        <v>-0.349</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0192</v>
+        <v>0.3262</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5838</v>
+        <v>-1.2165</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1919</v>
+        <v>-0.4328</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3919</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.4829</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.7034</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.2205</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9745</v>
+        <v>-1.285</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2473</v>
+        <v>-2.9736</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2218</v>
+        <v>1.6886</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5655</v>
+        <v>-0.0771</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1066</v>
+        <v>-1.3564</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4589</v>
+        <v>1.2793</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.349</v>
+        <v>0.4702</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3262</v>
+        <v>-0.4826</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6752</v>
+        <v>0.9527</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2165</v>
+        <v>-0.5473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4328</v>
+        <v>-0.8738</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7838000000000001</v>
+        <v>0.3266</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3758</v>
+        <v>0.7276</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5963000000000001</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2205</v>
+        <v>0.8228</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0071</v>
+        <v>0.3538</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0071</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1449</v>
+        <v>-1.3783</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2838</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8611</v>
+        <v>-0.7731</v>
       </c>
       <c r="G7" t="n">
         <v>-1.879</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0184</v>
+        <v>0.785</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1802</v>
+        <v>0.8587</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1618</v>
+        <v>-0.0737</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7005</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3654</v>
+        <v>-1.9493</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9156</v>
+        <v>-0.5289</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4498</v>
+        <v>-1.4204</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3029</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9668</v>
+        <v>1.3829</v>
       </c>
       <c r="T8" t="n">
-        <v>0.593</v>
+        <v>0.9797</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3739</v>
+        <v>0.4032</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9482</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1811</v>
+        <v>-2.9715</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5581</v>
+        <v>-2.8721</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6229</v>
+        <v>-0.0993</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0174</v>
+        <v>-2.4702</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5951</v>
+        <v>-0.1981</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4223</v>
+        <v>-2.2721</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4456</v>
+        <v>-2.8579</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6584</v>
+        <v>0.0959</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1039</v>
+        <v>-2.9538</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5719</v>
+        <v>0.3877</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2535</v>
+        <v>-0.294</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3184</v>
+        <v>0.6817</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8364</v>
+        <v>0.0419</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3849</v>
+        <v>-0.0142</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4515</v>
+        <v>0.0562</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2613</v>
+        <v>-2.9793</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0445</v>
+        <v>-2.3857</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2168</v>
+        <v>-0.5936</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4702</v>
+        <v>-3.0174</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1981</v>
+        <v>-0.5951</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2721</v>
+        <v>-2.4223</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8579</v>
+        <v>-1.4456</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0959</v>
+        <v>0.6584</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9538</v>
+        <v>-2.1039</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3877</v>
+        <v>-1.5719</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.294</v>
+        <v>-1.2535</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6817</v>
+        <v>-0.3184</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2479</v>
+        <v>1.0381</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1866</v>
+        <v>0.5573</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0613</v>
+        <v>0.4809</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0942</v>
+        <v>-3.0462</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9346</v>
+        <v>-3.2683</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1596</v>
+        <v>0.2221</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5136</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9323</v>
+        <v>0.1156</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8267</v>
+        <v>-0.1604</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1056</v>
+        <v>0.276</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5213</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8862</v>
+        <v>-4.5082</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5218</v>
+        <v>-5.3494</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.8411</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2664</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9193</v>
+        <v>-0.5414</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4476</v>
+        <v>-0.2752</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4717</v>
+        <v>-0.2661</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1168</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.7294</v>
+        <v>-11.0769</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.9343</v>
+        <v>-12.282</v>
       </c>
       <c r="F13" t="n">
-        <v>1.204900000000001</v>
+        <v>1.2049</v>
       </c>
       <c r="G13" t="n">
         <v>-12.675</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.715100000000001</v>
+        <v>-5.7151</v>
       </c>
       <c r="I13" t="n">
         <v>-6.9598</v>
@@ -1453,10 +1453,10 @@
         <v>-6.206700000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.063800000000001</v>
+        <v>-6.0638</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1430000000000005</v>
+        <v>-0.1430000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>1.0406</v>
@@ -1468,13 +1468,13 @@
         <v>11.4465</v>
       </c>
       <c r="S13" t="n">
-        <v>5.512700000000001</v>
+        <v>6.164999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8081</v>
+        <v>3.4605</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7047</v>
+        <v>2.704800000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-5.607699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3613</v>
+        <v>6.2209</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2562</v>
+        <v>4.149</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1052</v>
+        <v>2.0719</v>
       </c>
       <c r="G14" t="n">
         <v>4.3419</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.608</v>
+        <v>-0.7484</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0033</v>
+        <v>-0.1105</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6047</v>
+        <v>-0.638</v>
       </c>
       <c r="V14" t="n">
         <v>2.2112</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1327</v>
+        <v>3.9117</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6458</v>
+        <v>2.1635</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4869</v>
+        <v>1.7482</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9432</v>
+        <v>4.1447</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8506</v>
+        <v>0.6757</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0926</v>
+        <v>3.469</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6086</v>
+        <v>3.5693</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1978</v>
+        <v>0.6392</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4108</v>
+        <v>2.9301</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3347</v>
+        <v>0.5754</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3472</v>
+        <v>0.0366</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6818</v>
+        <v>0.5389</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7295</v>
+        <v>0.205</v>
       </c>
       <c r="T15" t="n">
-        <v>1.826</v>
+        <v>-0.3652</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0965</v>
+        <v>0.5703</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7076</v>
+        <v>-0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0314</v>
+        <v>3.908</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6277</v>
+        <v>1.2528</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4037</v>
+        <v>2.6552</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1447</v>
+        <v>4.9432</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6757</v>
+        <v>1.8506</v>
       </c>
       <c r="I16" t="n">
-        <v>3.469</v>
+        <v>3.0926</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5693</v>
+        <v>3.6086</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6392</v>
+        <v>2.1978</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9301</v>
+        <v>1.4108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5754</v>
+        <v>1.3347</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0366</v>
+        <v>-0.3472</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5389</v>
+        <v>1.6818</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6752</v>
+        <v>0.5048</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.901</v>
+        <v>0.433</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2258</v>
+        <v>0.0718</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8968</v>
+        <v>3.3651</v>
       </c>
       <c r="E17" t="n">
-        <v>1.513</v>
+        <v>1.8345</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3838</v>
+        <v>1.5306</v>
       </c>
       <c r="G17" t="n">
         <v>1.2408</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8248</v>
+        <v>-1.3565</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7829</v>
+        <v>-0.4615</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0418</v>
+        <v>-0.895</v>
       </c>
       <c r="V17" t="n">
         <v>3.2726</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4025</v>
+        <v>1.2909</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9574</v>
+        <v>-0.0443</v>
       </c>
       <c r="F18" t="n">
-        <v>1.445</v>
+        <v>1.3352</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1967</v>
+        <v>0.7522</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1876</v>
+        <v>-0.5777</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0091</v>
+        <v>1.33</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2253</v>
+        <v>-0.0396</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1469</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0784</v>
+        <v>0.5788</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9714</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>0.0407</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9307</v>
+        <v>0.7511</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9956</v>
+        <v>-0.4177</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6864</v>
+        <v>-0.0047</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6908</v>
+        <v>-0.4129</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2914</v>
+        <v>0.1238</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0.1238</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.852</v>
+        <v>1.2198</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3658</v>
+        <v>-0.2213</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2178</v>
+        <v>1.4411</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7522</v>
+        <v>2.1967</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5777</v>
+        <v>1.1876</v>
       </c>
       <c r="I19" t="n">
-        <v>1.33</v>
+        <v>1.0091</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0396</v>
+        <v>1.2253</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.1469</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5788</v>
+        <v>0.0784</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.9714</v>
       </c>
       <c r="N19" t="n">
         <v>0.0407</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7511</v>
+        <v>0.9307</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8566</v>
+        <v>-0.1871</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3262</v>
+        <v>0.5077</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5304</v>
+        <v>-0.6948</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1238</v>
+        <v>1.2914</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
         <v>0.1238</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3889</v>
+        <v>0.5836</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5684</v>
+        <v>-0.3694</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9573</v>
+        <v>0.9529</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2238</v>
+        <v>-0.3511</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1111</v>
+        <v>1.094</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1127</v>
+        <v>-1.4451</v>
       </c>
       <c r="J20" t="n">
-        <v>0.73</v>
+        <v>-0.2815</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6908</v>
+        <v>1.2044</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0392</v>
+        <v>-1.4859</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4938</v>
+        <v>-0.0696</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4203</v>
+        <v>-0.1105</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0735</v>
+        <v>0.0408</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9806</v>
+        <v>-0.2329</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>-0.7986</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2629</v>
+        <v>0.5657</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4599</v>
+        <v>1.7513</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1061</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1295</v>
+        <v>0.5254</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.798</v>
+        <v>-0.4612</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9275</v>
+        <v>0.9866</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3511</v>
+        <v>1.2238</v>
       </c>
       <c r="H21" t="n">
-        <v>1.094</v>
+        <v>1.1111</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4451</v>
+        <v>0.1127</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2815</v>
+        <v>0.73</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2044</v>
+        <v>0.6908</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4859</v>
+        <v>0.0392</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0696</v>
+        <v>0.4938</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1105</v>
+        <v>0.4203</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0408</v>
+        <v>0.0735</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.844</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2272</v>
+        <v>-0.6105</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5403</v>
+        <v>-0.2335</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7513</v>
+        <v>0.4599</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9746</v>
+        <v>-0.9159</v>
       </c>
       <c r="E22" t="n">
         <v>-0.5401</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4345</v>
+        <v>-0.3758</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4671</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7157</v>
+        <v>-0.657</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3895</v>
+        <v>-0.3308</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0298</v>
+        <v>-3.0909</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5514</v>
+        <v>-4.0156</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5215</v>
+        <v>0.9247</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7077</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1952</v>
+        <v>-0.2562</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0315</v>
+        <v>-0.4957</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1637</v>
+        <v>0.2395</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4611</v>
+        <v>-3.8603</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3814</v>
+        <v>-4.9527</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9202</v>
+        <v>1.0925</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6425</v>
@@ -2326,13 +2326,13 @@
         <v>0.6244</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6948</v>
+        <v>-0.0939</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.901</v>
+        <v>-0.4724</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2062</v>
+        <v>0.3785</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7076</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.7296</v>
+        <v>13.1583</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.205000000000002</v>
+        <v>-1.204800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>12.9344</v>
+        <v>14.3631</v>
       </c>
       <c r="G25" t="n">
         <v>12.6749</v>
@@ -2380,7 +2380,7 @@
         <v>6.206399999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>6.0637</v>
+        <v>6.063700000000001</v>
       </c>
       <c r="L25" t="n">
         <v>0.1427999999999994</v>
@@ -2392,7 +2392,7 @@
         <v>-0.3488</v>
       </c>
       <c r="O25" t="n">
-        <v>6.817099999999999</v>
+        <v>6.8171</v>
       </c>
       <c r="P25" t="n">
         <v>-1.0406</v>
@@ -2404,16 +2404,16 @@
         <v>10.406</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.512799999999999</v>
+        <v>-4.0839</v>
       </c>
       <c r="T25" t="n">
         <v>-2.7046</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.808</v>
+        <v>-1.3792</v>
       </c>
       <c r="V25" t="n">
-        <v>5.607599999999999</v>
+        <v>5.607600000000001</v>
       </c>
       <c r="W25" t="n">
         <v>6.7397</v>
